--- a/EN_labeled.xlsx
+++ b/EN_labeled.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Domanda1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Domanda 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Domanda 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domanda1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domanda 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domanda 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -638,202 +638,202 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>D1_attività uso della tecnologia</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D1_scienza</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>D1_misure</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>D1_storytelling</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>D1_geografia</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>D1_coding unplugged</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>D1_attività unplugged</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>D1_decomposizione</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>D1_geometria</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>D1_sviluppo iterativo</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>D1_verifica e correzione</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>D1_ricerca di informazioni</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>D1_pixel art</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>D1_sequenza</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>D1_programmazione</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>D1_coding</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>D1_altre attività</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>D1_aritmetica</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>D1_attività sviluppo contenuti</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>D1_attività ludico-motoria</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>D1_intelligenza artificiale</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>D1_techno-CLIL</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>D1_riferimenti topologici</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>D1_strutture dati</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>D1_lettura codice</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>D1_pseudo-linguaggio</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>D1_labirinto</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>D1_istruzioni di base</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>D1_esecuzione di istruzioni</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>D1_coding analogico</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>D1_attività costruzione di mappe</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>D1_conversazione collaborativa / collaborazione</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>D1_pensiero critico</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>D1_pensiero creativo</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>D1_rianalizzare</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>D1_pensiero computazionale</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>D1_risoluzione di problemi</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>D1_videotutorial</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>D1_pianificazione</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
           <t>D1_uso della tecnologia</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>D1_scienza</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>D1_misure</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>D1_storytelling</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>D1_geografia</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>D1_coding unplugged</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>D1_attività unplugged</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>D1_decomposizione</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>D1_geometria</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>D1_sviluppo iterativo</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>D1_verifica e correzione</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>D1_ricerca di informazioni</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>D1_pixel art</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>D1_sequenza</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>D1_programmazione</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>D1_coding</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>D1_altre attività</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>D1_aritmetica</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>D1_sviluppo contenuti2</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>D1_ludico-motoria2</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>D1_intelligenza artificiale</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>D1_techno-CLIL</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>D1_riferimenti topologici</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>D1_strutture dati</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>D1_lettura codice</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>D1_pseudo-linguaggio</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>D1_labirinto</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>D1_istruzioni di base</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>D1_esecuzione di istruzioni</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>D1_coding analogico</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>D1_costruzione mappe</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>D1_conversazione collaborativa / collaborazione</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>D1_pensiero critico</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>D1_pensiero creativo</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>D1_rianalizzare</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>D1_pensiero computazionale</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>D1_risoluzione di problemi</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>D1_videotutorial</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>D1_pianificazione</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>D1_uso della tecnologia2</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -3778,7 +3778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP63"/>
+  <dimension ref="A1:CP62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>D2_ comprensione dei comandi di progrmmazione</t>
+          <t>D2_comprensione dei comandi di programmazione</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
@@ -6052,217 +6052,6 @@
         <is>
           <t>X</t>
         </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>QUANTE USATE</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" t="n">
-        <v>15</v>
-      </c>
-      <c r="F63" t="n">
-        <v>8</v>
-      </c>
-      <c r="G63" t="n">
-        <v>3</v>
-      </c>
-      <c r="H63" t="n">
-        <v>4</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" t="n">
-        <v>2</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
-        <v>4</v>
-      </c>
-      <c r="P63" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>3</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S63" t="n">
-        <v>7</v>
-      </c>
-      <c r="T63" t="n">
-        <v>13</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1</v>
-      </c>
-      <c r="W63" t="n">
-        <v>4</v>
-      </c>
-      <c r="X63" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>31</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ63" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO63" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6276,7 +6065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX63"/>
+  <dimension ref="A1:CX62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6429,7 +6218,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>D3_osservazione, memoria, analisi</t>
+          <t>D3_osservazione/ memoria/ analisi</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -7916,7 +7705,11 @@
 competenze linguistiche, logico- matematiche, spazialità, Problem solving</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>X</t>
@@ -8278,244 +8071,6 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>QUANTE USATE</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="n">
-        <v>7</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="n">
-        <v>3</v>
-      </c>
-      <c r="H63" t="n">
-        <v>7</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>11</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" t="n">
-        <v>2</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1</v>
-      </c>
-      <c r="X63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU63" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>3</v>
-      </c>
-      <c r="BZ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB63" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD63" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF63" t="n">
-        <v>3</v>
-      </c>
-      <c r="CG63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CH63" t="n">
-        <v>2</v>
-      </c>
-      <c r="CI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ63" t="n">
-        <v>3</v>
-      </c>
-      <c r="CK63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN63" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO63" t="n">
-        <v>3</v>
-      </c>
-      <c r="CP63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX63" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
